--- a/auto_script.xlsx
+++ b/auto_script.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_Project_EMIC\7_ToolTest\BoardTest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Firmware_TNT\6_DA_2026\BoardTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5F9390-1C26-44EF-B9F7-EECD52739CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,44 +25,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t>STT</t>
   </si>
   <si>
-    <t>Serial module</t>
-  </si>
-  <si>
     <t>Hạng muc</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>R/W</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
-    <t>Kiểu dữ liệu gửi</t>
-  </si>
-  <si>
-    <t>Kiểu dữ liệu nhận</t>
-  </si>
-  <si>
-    <t>Giá trị gửi</t>
-  </si>
-  <si>
-    <t>Giá trị nhận</t>
-  </si>
-  <si>
-    <t>hex array</t>
-  </si>
-  <si>
     <t>Type pack</t>
   </si>
   <si>
@@ -73,13 +46,160 @@
   </si>
   <si>
     <t>Param</t>
+  </si>
+  <si>
+    <t>Đọc kiểm tra</t>
+  </si>
+  <si>
+    <t>OptHesRead</t>
+  </si>
+  <si>
+    <t>Param Type</t>
+  </si>
+  <si>
+    <t>Ghi</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>260909010203</t>
+  </si>
+  <si>
+    <t>Đọc ban đầu</t>
+  </si>
+  <si>
+    <t>Chờ(giây)</t>
+  </si>
+  <si>
+    <t>Len</t>
+  </si>
+  <si>
+    <t>Payload Send</t>
+  </si>
+  <si>
+    <t>Payload Rec</t>
+  </si>
+  <si>
+    <t>ACK</t>
+  </si>
+  <si>
+    <t>NACK</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Imp Data</t>
+  </si>
+  <si>
+    <t>Exp Data</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Meter Serial</t>
+  </si>
+  <si>
+    <t>Module Serial</t>
+  </si>
+  <si>
+    <t>Qccid</t>
+  </si>
+  <si>
+    <t>IMSI</t>
+  </si>
+  <si>
+    <t>APN</t>
+  </si>
+  <si>
+    <t>Nhà mạng</t>
+  </si>
+  <si>
+    <t>Ip Port Sever</t>
+  </si>
+  <si>
+    <t>Ip Module</t>
+  </si>
+  <si>
+    <t>Type WM</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>L/vong</t>
+  </si>
+  <si>
+    <t>Latch Period</t>
+  </si>
+  <si>
+    <t>Push Method</t>
+  </si>
+  <si>
+    <t>Push Period</t>
+  </si>
+  <si>
+    <t>Push Timestamp1</t>
+  </si>
+  <si>
+    <t>Push Timestamp2</t>
+  </si>
+  <si>
+    <t>Số tháng còn lại của Pin</t>
+  </si>
+  <si>
+    <t>Temp</t>
+  </si>
+  <si>
+    <t>Voltage</t>
+  </si>
+  <si>
+    <t>Num Reset</t>
+  </si>
+  <si>
+    <t>Rssi</t>
+  </si>
+  <si>
+    <t>Cấu hình sự kiện</t>
+  </si>
+  <si>
+    <t>ClearData</t>
+  </si>
+  <si>
+    <t>Kich hoat thiết bị</t>
+  </si>
+  <si>
+    <t>Push Data</t>
+  </si>
+  <si>
+    <t>Reset Module</t>
+  </si>
+  <si>
+    <t>LatData Index</t>
+  </si>
+  <si>
+    <t>PushData Index</t>
+  </si>
+  <si>
+    <t>LatchEvent Index</t>
+  </si>
+  <si>
+    <t>PushEvent Index</t>
+  </si>
+  <si>
+    <t>Nb_Info</t>
+  </si>
+  <si>
+    <t>Result</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,8 +228,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,8 +256,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8D08D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD965"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFD9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF2CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -146,26 +304,211 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,122 +788,242 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:K15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:U16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="7" width="17.140625" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" customWidth="1"/>
+    <col min="13" max="13" width="5.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" customWidth="1"/>
+    <col min="16" max="16" width="6" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" customWidth="1"/>
+    <col min="18" max="18" width="16.28515625" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="2" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="19"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="23"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="10"/>
+      <c r="P4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="10"/>
+      <c r="T4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U4" s="3">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4">
+        <v>6</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>6</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="L5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="2">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="S5" s="2"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2649000043</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="2" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>3</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="3">
-        <v>2649000043</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>4</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -568,117 +1031,530 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="2"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="P2:R2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:C38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="13">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="13">
+        <v>2</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="13">
+        <v>3</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="13">
+        <v>4</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="13">
+        <v>6</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="13">
+        <v>7</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="13">
+        <v>8</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="13">
+        <v>9</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="13">
+        <v>10</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="13">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="13">
+        <v>12</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="13">
+        <v>13</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="13">
+        <v>14</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="13">
+        <v>15</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="13">
+        <v>16</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="13">
+        <v>17</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="13">
+        <v>18</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="13">
+        <v>19</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="13">
+        <v>20</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="13">
+        <v>21</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="15"/>
+      <c r="C24" s="14"/>
+    </row>
+    <row r="25" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="13">
+        <v>22</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="13">
+        <v>23</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="13">
+        <v>24</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="13">
+        <v>25</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="13">
+        <v>26</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="13">
+        <v>27</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="13">
+        <v>28</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="13">
+        <v>29</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="16">
+        <v>30</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="16">
+        <v>31</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="16">
+        <v>32</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="16">
+        <v>33</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="16">
+        <v>34</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="16">
+        <v>35</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>